--- a/results/hsp90_class_enrichment/hsp90_class_enrichment.xlsx
+++ b/results/hsp90_class_enrichment/hsp90_class_enrichment.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,20 +456,30 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>PERMUTATION_UNIVERSE_N</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>PERMUTATIONS</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>RANDOM_SEED</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>EMPIRICAL_P_VALUE</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>MEAN_PERMUTED_MEDIAN</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>SD_PERMUTED_MEDIAN</t>
         </is>
@@ -498,15 +508,21 @@
         <v>0.07274749721913237</v>
       </c>
       <c r="H2" t="n">
+        <v>1407</v>
+      </c>
+      <c r="I2" t="n">
         <v>10000</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
+        <v>42</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.999000099990002e-05</v>
+      </c>
+      <c r="L2" t="n">
         <v>-0.007604531311233003</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.06325340432836568</v>
       </c>
     </row>
